--- a/result/morris/morris_first_inf_ONLY_MAE_N256_seed123.xlsx
+++ b/result/morris/morris_first_inf_ONLY_MAE_N256_seed123.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D13"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -453,65 +453,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>dispersal__rain_min</t>
+          <t>zoospore_alive__vpd</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>11.89105902777777</v>
+        <v>-8.02191840277778</v>
       </c>
       <c r="C2" t="n">
-        <v>18.48242187500001</v>
+        <v>17.41579861111111</v>
       </c>
       <c r="D2" t="n">
-        <v>31.2067628962774</v>
+        <v>25.17890720621237</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>zoospore_alive__vpd</t>
+          <t>dispersal__rain_min</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-10.6591796875</v>
+        <v>1.079752604166667</v>
       </c>
       <c r="C3" t="n">
-        <v>17.4211154513889</v>
+        <v>15.02159288194445</v>
       </c>
       <c r="D3" t="n">
-        <v>28.51271733160276</v>
+        <v>23.44129569416743</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>infection__infection_condition</t>
+          <t>thresholds__min_spores</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12.54329427083333</v>
+        <v>2.479817708333334</v>
       </c>
       <c r="C4" t="n">
-        <v>17.38639322916668</v>
+        <v>13.02235243055557</v>
       </c>
       <c r="D4" t="n">
-        <v>23.0489360474682</v>
+        <v>20.14842309506301</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mp_tmp__rh_wet_night</t>
+          <t>infection__infection_condition</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.673611111111104</v>
+        <v>4.880859375000005</v>
       </c>
       <c r="C5" t="n">
-        <v>15.787109375</v>
+        <v>12.61284722222222</v>
       </c>
       <c r="D5" t="n">
-        <v>22.14618445328179</v>
+        <v>17.93672734913988</v>
       </c>
     </row>
     <row r="6">
@@ -521,29 +521,29 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05457899305555517</v>
+        <v>0.1392144097222223</v>
       </c>
       <c r="C6" t="n">
-        <v>5.0693359375</v>
+        <v>8.084960937500004</v>
       </c>
       <c r="D6" t="n">
-        <v>11.26612143839068</v>
+        <v>15.06206326211871</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>sporulation__MP_min</t>
+          <t>mp_tmp__rh_wet_night</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.040690104166666</v>
+        <v>2.42947048611111</v>
       </c>
       <c r="C7" t="n">
-        <v>3.686740451388888</v>
+        <v>7.696831597222226</v>
       </c>
       <c r="D7" t="n">
-        <v>8.296094662459691</v>
+        <v>12.80056242823363</v>
       </c>
     </row>
     <row r="8">
@@ -553,93 +553,109 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7919921875</v>
+        <v>3.244574652777778</v>
       </c>
       <c r="C8" t="n">
-        <v>2.398328993055555</v>
+        <v>4.912977430555557</v>
       </c>
       <c r="D8" t="n">
-        <v>7.639738705916962</v>
+        <v>11.19617415213992</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>deposition__rain_min</t>
+          <t>sporulation__Topt</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.717881944444445</v>
+        <v>-0.2113715277777778</v>
       </c>
       <c r="C9" t="n">
-        <v>1.98654513888889</v>
+        <v>3.781250000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>6.782093020292418</v>
+        <v>9.683219140675801</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>sporulation__Topt</t>
+          <t>sporulation__Tmin</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>-0.4064670138888889</v>
+        <v>-0.5110677083333333</v>
       </c>
       <c r="C10" t="n">
-        <v>1.636067708333333</v>
+        <v>3.03146701388889</v>
       </c>
       <c r="D10" t="n">
-        <v>7.133064026752638</v>
+        <v>9.090353326474311</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>incubation__spl_end</t>
+          <t>zoospore_alive__rain</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7125651041666665</v>
+        <v>0.8395182291666667</v>
       </c>
       <c r="C11" t="n">
-        <v>1.223198784722222</v>
+        <v>1.695421006944444</v>
       </c>
       <c r="D11" t="n">
-        <v>1.272081718456729</v>
+        <v>6.86959362668868</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>zoospore_alive__rain</t>
+          <t>sporulation__MP_min</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0224609374999999</v>
+        <v>-0.1742621527777778</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7987196180555556</v>
+        <v>1.450086805555556</v>
       </c>
       <c r="D12" t="n">
-        <v>2.836895759649767</v>
+        <v>4.728657302995888</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>sporulation__Tmin</t>
+          <t>deposition__rain_min</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.4656032986111111</v>
+        <v>0.7989366319444443</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7705078125</v>
+        <v>1.405924479166666</v>
       </c>
       <c r="D13" t="n">
-        <v>5.854822557722201</v>
+        <v>4.995536759111143</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>incubation__spl_end</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>0.449001736111111</v>
+      </c>
+      <c r="C14" t="n">
+        <v>1.130208333333332</v>
+      </c>
+      <c r="D14" t="n">
+        <v>1.327336629861848</v>
       </c>
     </row>
   </sheetData>
